--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104713_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104713_W29.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2242</v>
+        <v>4.2838</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9848</v>
+        <v>6.0168</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7605</v>
+        <v>-1.733</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9095</v>
+        <v>-0.9075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3434</v>
+        <v>0.3419</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2529</v>
+        <v>-1.2494</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6441</v>
+        <v>2.6328</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8612</v>
+        <v>1.8508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7829</v>
+        <v>0.782</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5536</v>
+        <v>-3.5403</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5178</v>
+        <v>-1.5089</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0358</v>
+        <v>-2.0314</v>
       </c>
       <c r="P2" t="n">
-        <v>3.4078</v>
+        <v>3.4145</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4078</v>
+        <v>3.4145</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6347</v>
+        <v>0.6873</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0669</v>
+        <v>0.1155</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5678</v>
+        <v>0.5718</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2738</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.1825</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3274</v>
+        <v>1.9335</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6745</v>
+        <v>1.0295</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0019</v>
+        <v>0.904</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2521</v>
+        <v>0.5991</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0548</v>
+        <v>0.8302</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3069</v>
+        <v>-0.2311</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7802</v>
+        <v>1.7579</v>
       </c>
       <c r="K3" t="n">
-        <v>1.227</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5532</v>
+        <v>0.8411</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0323</v>
+        <v>-1.1588</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1722</v>
+        <v>-0.0866</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8601</v>
+        <v>-1.0722</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3631</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4991</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1698</v>
+        <v>-0.3485</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3187</v>
+        <v>-0.135</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1489</v>
+        <v>-0.2135</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3862</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3178</v>
+        <v>1.4021</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5707</v>
+        <v>-0.214</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8885</v>
+        <v>1.6161</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2518</v>
+        <v>-0.2472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7055</v>
+        <v>0.0596</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9572</v>
+        <v>-0.3069</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0979</v>
+        <v>1.7747</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6072</v>
+        <v>1.2238</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5092</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3497</v>
+        <v>-2.0219</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-1.1642</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.448</v>
+        <v>-0.8578</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9534</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9534</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7755</v>
+        <v>-0.1035</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6686</v>
+        <v>-0.8506</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4441</v>
+        <v>0.7471</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1594</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1594</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2134</v>
+        <v>0.9193</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5714</v>
+        <v>-0.4651</v>
       </c>
       <c r="F5" t="n">
-        <v>0.642</v>
+        <v>1.3844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6021</v>
+        <v>-2.2457</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8317</v>
+        <v>0.7114</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2297</v>
+        <v>-2.957</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7674</v>
+        <v>0.0905</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9219000000000001</v>
+        <v>1.603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8455</v>
+        <v>-1.5125</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1654</v>
+        <v>-2.3362</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0902</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0752</v>
+        <v>-1.4446</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1359</v>
+        <v>2.9592</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2719</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0702</v>
+        <v>0.3635</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6057</v>
+        <v>-0.5557</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4645</v>
+        <v>0.9192</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5456</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5456</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. ALDERETE</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2436</v>
+        <v>-0.4928</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.537</v>
+        <v>-0.0835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2934</v>
+        <v>-0.4094</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6308</v>
+        <v>-0.9482</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8445</v>
+        <v>-0.9136</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7862</v>
+        <v>-0.0346</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9095</v>
+        <v>0.6148</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>-0.1519</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.944</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.5629</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8791</v>
+        <v>-0.7617</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1578</v>
+        <v>-0.8012</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9087</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9087</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4784</v>
+        <v>-0.1593</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3725</v>
+        <v>-0.1048</v>
       </c>
       <c r="U6" t="n">
-        <v>0.106</v>
+        <v>-0.0545</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2933</v>
+        <v>-0.8215</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2837</v>
+        <v>-1.8751</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.577</v>
+        <v>1.0536</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9479</v>
+        <v>-2.6015</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9159</v>
+        <v>-1.7517</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.032</v>
+        <v>-0.8499</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6214</v>
+        <v>-0.3507</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1495</v>
+        <v>-0.573</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7709</v>
+        <v>0.2223</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5693</v>
+        <v>-2.2508</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7664</v>
+        <v>-1.1786</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2272</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3631</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0412</v>
+        <v>-0.1988</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2526</v>
+        <v>-0.544</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2115</v>
+        <v>0.3452</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3862</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5456</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>H. ALDERETE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5079</v>
+        <v>-0.8405</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9935</v>
+        <v>-1.0141</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5144</v>
+        <v>0.1736</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0599</v>
+        <v>-1.6301</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1976</v>
+        <v>-0.8418</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2574</v>
+        <v>-0.7883</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9262</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3492</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2754</v>
+        <v>-0.9463</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8663</v>
+        <v>-0.7184</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8484</v>
+        <v>-0.8763</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0179</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.9981</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.8156</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8175</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7935</v>
+        <v>-0.1209</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2591</v>
+        <v>-0.1024</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5344</v>
+        <v>-0.0185</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6369</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6369</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,37 +1111,37 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6129</v>
+        <v>-1.6153</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9217</v>
+        <v>-0.9258</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6913</v>
+        <v>-0.6895</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3163</v>
+        <v>-1.3179</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5274</v>
+        <v>-0.5283</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7829</v>
+        <v>-0.7864</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006</v>
+        <v>0.0033</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7889</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5335</v>
+        <v>-0.5315</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5335</v>
+        <v>-0.5315</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2966</v>
+        <v>-0.2973</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1578</v>
+        <v>-0.1579</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8061</v>
+        <v>-1.8504</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5583</v>
+        <v>-1.6356</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7522</v>
+        <v>-0.2148</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5948</v>
+        <v>1.0416</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7506</v>
+        <v>-2.2096</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8442</v>
+        <v>3.2512</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3324</v>
+        <v>3.8965</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5634</v>
+        <v>-0.3704</v>
       </c>
       <c r="L10" t="n">
-        <v>0.231</v>
+        <v>4.2669</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2624</v>
+        <v>-2.8549</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1872</v>
+        <v>-1.8392</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0752</v>
+        <v>-1.0157</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8175</v>
+        <v>-5.0079</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-6.8289</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9534</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1882</v>
+        <v>0.4817</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2493</v>
+        <v>-0.3373</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0611</v>
+        <v>0.819</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1594</v>
+        <v>1.6342</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1594</v>
+        <v>1.6342</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7278</v>
+        <v>-3.2969</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1847</v>
+        <v>0.168</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5431</v>
+        <v>-3.4649</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9715</v>
+        <v>-1.965</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1248</v>
+        <v>-0.1211</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8468</v>
+        <v>-1.8439</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1383</v>
+        <v>0.1379</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1843</v>
+        <v>-2.1774</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.263</v>
+        <v>-0.259</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9213</v>
+        <v>-1.9184</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4821</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3975</v>
+        <v>-0.0444</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0847</v>
+        <v>-0.0207</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.9557</v>
+        <v>-1.9497</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9557</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9329</v>
+        <v>-4.6675</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.564</v>
+        <v>-2.3409</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3689</v>
+        <v>-2.3266</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.9267</v>
+        <v>-3.9251</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5335</v>
+        <v>-0.5315</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3933</v>
+        <v>-3.3936</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1424</v>
+        <v>-2.1478</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0752</v>
+        <v>0.0722</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2176</v>
+        <v>-2.22</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7843</v>
+        <v>-1.7774</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1757</v>
+        <v>-1.1736</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.484</v>
+        <v>-0.2173</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5363</v>
+        <v>-0.3022</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0523</v>
+        <v>0.0849</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.041700000000001</v>
+        <v>-5.046200000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1645</v>
+        <v>-1.339799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8772</v>
+        <v>-3.7065</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.1394</v>
+        <v>-14.1475</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.9589</v>
+        <v>-4.9545</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.1807</v>
+        <v>-9.193100000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>6.8828</v>
+        <v>6.7829</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8093</v>
+        <v>4.747</v>
       </c>
       <c r="L13" t="n">
-        <v>2.073800000000001</v>
+        <v>2.035899999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.0224</v>
+        <v>-20.9305</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.7681</v>
+        <v>-9.7013</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.2543</v>
+        <v>-11.2292</v>
       </c>
       <c r="P13" t="n">
-        <v>6.8155</v>
+        <v>6.829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.4951</v>
+        <v>-12.5199</v>
       </c>
       <c r="R13" t="n">
-        <v>19.3109</v>
+        <v>19.3487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03240000000000021</v>
+        <v>0.02180000000000004</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9638</v>
+        <v>-3.0003</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9961</v>
+        <v>3.0221</v>
       </c>
       <c r="V13" t="n">
-        <v>2.249899999999999</v>
+        <v>2.2505</v>
       </c>
       <c r="W13" t="n">
-        <v>7.412</v>
+        <v>7.397</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.162100000000001</v>
+        <v>-5.1467</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5823</v>
+        <v>7.6192</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6705</v>
+        <v>7.5297</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0882</v>
+        <v>0.0896</v>
       </c>
       <c r="G14" t="n">
-        <v>6.0948</v>
+        <v>6.092</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.3487</v>
+        <v>-2.3466</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4436</v>
+        <v>8.438499999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>7.3221</v>
+        <v>7.307</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3644</v>
+        <v>-1.3692</v>
       </c>
       <c r="L14" t="n">
-        <v>8.686500000000001</v>
+        <v>8.6762</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2273</v>
+        <v>-1.215</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9843</v>
+        <v>-0.9774</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.243</v>
+        <v>-0.2377</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3281</v>
+        <v>0.3695</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2336</v>
+        <v>0.1136</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0944</v>
+        <v>0.2559</v>
       </c>
       <c r="V14" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0882</v>
+        <v>2.671</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6176</v>
+        <v>4.2493</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5294</v>
+        <v>-1.5783</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5379</v>
+        <v>1.5377</v>
       </c>
       <c r="H15" t="n">
-        <v>2.653</v>
+        <v>2.6484</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1151</v>
+        <v>-1.1108</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1333</v>
+        <v>3.1254</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0588</v>
+        <v>3.0509</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5954</v>
+        <v>-1.5877</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4058</v>
+        <v>-0.4025</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1897</v>
+        <v>-1.1852</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.255</v>
+        <v>-0.1626</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2336</v>
+        <v>-0.1233</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0213</v>
+        <v>-0.0392</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8483</v>
+        <v>2.515</v>
       </c>
       <c r="E16" t="n">
-        <v>1.495</v>
+        <v>1.8284</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3533</v>
+        <v>0.6866</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6038</v>
+        <v>2.6011</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-0.9993</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6023</v>
+        <v>3.6004</v>
       </c>
       <c r="J16" t="n">
-        <v>3.601</v>
+        <v>3.5872</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3448</v>
+        <v>-0.3522</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9458</v>
+        <v>3.9394</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9972</v>
+        <v>-0.9861</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.6471</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0508</v>
+        <v>-0.382</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9023</v>
+        <v>-0.5508</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1485</v>
+        <v>0.1688</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6787</v>
+        <v>0.9558</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3551</v>
+        <v>0.4613</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3237</v>
+        <v>0.4944</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2999</v>
+        <v>1.2984</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9077</v>
+        <v>1.9044</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6078</v>
+        <v>-0.6061</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2763</v>
+        <v>1.2676</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0279</v>
+        <v>2.02</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0235</v>
+        <v>0.0308</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1203</v>
+        <v>-0.1155</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1438</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2115</v>
+        <v>0.064</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.5786</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4826</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3709</v>
+        <v>0.9311</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0346</v>
+        <v>1.2254</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3364</v>
+        <v>-0.2943</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3501</v>
+        <v>1.4363</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0346</v>
+        <v>-0.7016</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3156</v>
+        <v>2.1378</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0346</v>
+        <v>1.4067</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>0.1034</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.3033</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3156</v>
+        <v>0.0296</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.805</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3156</v>
+        <v>0.8345</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0208</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1813</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0208</v>
+        <v>0.0827</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.307</v>
+        <v>0.4026</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9921</v>
+        <v>0.0345</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6851</v>
+        <v>0.3681</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4292</v>
+        <v>0.3503</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7078</v>
+        <v>0.0345</v>
       </c>
       <c r="I19" t="n">
-        <v>2.137</v>
+        <v>0.3159</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4085</v>
+        <v>0.0345</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1037</v>
+        <v>0.0345</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3048</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0207</v>
+        <v>0.3159</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8115</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.3159</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6816</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6816</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7126</v>
+        <v>0.0523</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4164</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2961</v>
+        <v>0.0523</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2361</v>
+        <v>-0.7248</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1039</v>
+        <v>-1.9597</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8679</v>
+        <v>1.2349</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0262</v>
+        <v>3.0289</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9903</v>
+        <v>1.9902</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0359</v>
+        <v>1.0387</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8073</v>
+        <v>2.7977</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5464</v>
+        <v>2.5371</v>
       </c>
       <c r="L20" t="n">
-        <v>0.261</v>
+        <v>0.2607</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2189</v>
+        <v>0.2311</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5561</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7749</v>
+        <v>0.778</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.9069</v>
+        <v>-5.9184</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1221</v>
+        <v>0.6412</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7449</v>
+        <v>-0.0863</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3771</v>
+        <v>0.7275</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7932</v>
+        <v>-1.0154</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0321</v>
+        <v>-0.3339</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8253</v>
+        <v>-0.6816</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2614</v>
+        <v>-0.2548</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3118</v>
+        <v>0.3154</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5732</v>
+        <v>-0.5702</v>
       </c>
       <c r="J21" t="n">
-        <v>1.212</v>
+        <v>1.2064</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0256</v>
+        <v>1.0202</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1864</v>
+        <v>0.1862</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4735</v>
+        <v>-1.4612</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7139</v>
+        <v>-0.7048</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2133</v>
+        <v>-0.4436</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.044</v>
+        <v>-0.4021</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1693</v>
+        <v>-0.0414</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2486</v>
+        <v>-2.104</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2218</v>
+        <v>-1.876</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0268</v>
+        <v>-0.228</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5289</v>
+        <v>-1.5245</v>
       </c>
       <c r="H22" t="n">
-        <v>1.405</v>
+        <v>1.4069</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.9339</v>
+        <v>-2.9314</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3918</v>
+        <v>-0.3961</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0369</v>
+        <v>1.0342</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4287</v>
+        <v>-1.4303</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1371</v>
+        <v>-1.1284</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3681</v>
+        <v>0.3727</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5052</v>
+        <v>-1.5011</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0828</v>
+        <v>0.0547</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.3417</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6113</v>
+        <v>0.3964</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5136</v>
+        <v>-2.4354</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5947</v>
+        <v>-3.3742</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0811</v>
+        <v>0.9388</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5984</v>
+        <v>-0.6016</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1284</v>
+        <v>-0.1342</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.47</v>
+        <v>-0.4674</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6098</v>
+        <v>-0.6192</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1045</v>
+        <v>0.0959</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7143</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0114</v>
+        <v>0.0176</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2329</v>
+        <v>-0.2301</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2207</v>
+        <v>0.3044</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4858</v>
+        <v>-0.251</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7066</v>
+        <v>0.5554</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0424</v>
+        <v>-2.9792</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3993</v>
+        <v>-4.0783</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3569</v>
+        <v>1.0992</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1863</v>
+        <v>0.1839</v>
       </c>
       <c r="H24" t="n">
-        <v>0.84</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6538</v>
+        <v>-0.6523</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2286</v>
+        <v>1.2134</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5389</v>
+        <v>1.5266</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3102</v>
+        <v>-0.3132</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0423</v>
+        <v>-1.0295</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6988</v>
+        <v>-0.6904</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.9981</v>
+        <v>-5.0079</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.9069</v>
+        <v>-5.9184</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.292</v>
+        <v>0.3684</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9717</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2637</v>
+        <v>0.9889</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4775</v>
+        <v>1.4764</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.041500000000001</v>
+        <v>5.835900000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8773</v>
+        <v>3.706500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1645</v>
+        <v>2.1294</v>
       </c>
       <c r="G25" t="n">
-        <v>14.1395</v>
+        <v>14.1477</v>
       </c>
       <c r="H25" t="n">
-        <v>4.959</v>
+        <v>4.9543</v>
       </c>
       <c r="I25" t="n">
-        <v>9.1806</v>
+        <v>9.193099999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>21.0221</v>
+        <v>20.9306</v>
       </c>
       <c r="K25" t="n">
-        <v>9.768099999999999</v>
+        <v>9.701400000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>11.2543</v>
+        <v>11.2292</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.882700000000001</v>
+        <v>-6.7829</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.8092</v>
+        <v>-4.747000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.0737</v>
+        <v>-2.0361</v>
       </c>
       <c r="P25" t="n">
-        <v>-6.8154</v>
+        <v>-6.8288</v>
       </c>
       <c r="Q25" t="n">
-        <v>-19.3109</v>
+        <v>-19.3487</v>
       </c>
       <c r="R25" t="n">
-        <v>12.4951</v>
+        <v>12.5197</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.03229999999999994</v>
+        <v>0.7677</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.996300000000001</v>
+        <v>-3.022</v>
       </c>
       <c r="U25" t="n">
-        <v>2.9639</v>
+        <v>3.7899</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.25</v>
+        <v>-2.2504</v>
       </c>
       <c r="W25" t="n">
-        <v>5.1622</v>
+        <v>5.1466</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.4121</v>
+        <v>-7.3971</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104713_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104713_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.1467</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104713_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.3971</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
